--- a/SGC-CKN/Excel/12bd2238-5dc8-459d-a641-da6acac5da71_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-30_D800_23-03-2026.xlsx
+++ b/SGC-CKN/Excel/12bd2238-5dc8-459d-a641-da6acac5da71_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-30_D800_23-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="75">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P7-30</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t>KCL-0004</t>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>KCL-0002</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -112,7 +112,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">13h05
@@ -191,7 +191,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">20h37
@@ -205,7 +205,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1.Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xám, xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">23h00
@@ -213,9 +213,6 @@
   </si>
   <si>
     <t>9</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">23h00
@@ -1499,13 +1496,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="E19" s="34" t="s">
         <v>63</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>64</v>
       </c>
       <c r="F19" s="32">
         <v>-39.50999999999999</v>
@@ -1523,12 +1520,12 @@
         <v>0.6</v>
       </c>
       <c r="K19" s="33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B22" s="35"/>
       <c r="C22" s="35"/>
@@ -1634,31 +1631,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1901,7 +1898,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D10" s="32">
         <v>1</v>
@@ -1924,7 +1921,7 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B11" s="37" t="s">
         <v>44</v>

--- a/SGC-CKN/Excel/12bd2238-5dc8-459d-a641-da6acac5da71_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-30_D800_23-03-2026.xlsx
+++ b/SGC-CKN/Excel/12bd2238-5dc8-459d-a641-da6acac5da71_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-30_D800_23-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="72">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t>KCL-0002</t>
+    <t/>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">11h01
@@ -126,9 +126,6 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
-  </si>
-  <si>
     <t xml:space="preserve">13h29
 21/03/2026</t>
   </si>
@@ -154,13 +151,10 @@
 21/03/2026</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">17h35
@@ -172,9 +166,6 @@
   </si>
   <si>
     <t>6</t>
-  </si>
-  <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">19h51
@@ -260,7 +251,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -326,18 +317,13 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF164E63"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF831843"/>
+      <color rgb="FF164E63"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -354,7 +340,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -423,17 +409,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5F3FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBCFE8"/>
+        <fgColor rgb="FFA5F3FC"/>
       </patternFill>
     </fill>
     <fill>
@@ -529,7 +510,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -615,31 +596,22 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1286,13 +1258,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="E13" s="15" t="s">
         <v>37</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="13">
         <v>-10.11</v>
@@ -1310,24 +1282,24 @@
         <v>3.1</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="E14" s="18" t="s">
         <v>42</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>43</v>
       </c>
       <c r="F14" s="16">
         <v>-17.91</v>
@@ -1345,24 +1317,24 @@
         <v>3.04</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>46</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>48</v>
       </c>
       <c r="F15" s="19">
         <v>-22.21</v>
@@ -1380,163 +1352,163 @@
         <v>2</v>
       </c>
       <c r="K15" s="20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="20" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="D16" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" s="22">
+      <c r="F16" s="19">
         <v>-26.71</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="19">
         <v>-35.709999999999994</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="19">
         <v>0.73</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="19">
         <v>9</v>
       </c>
       <c r="J16" s="12">
         <v>12.27</v>
       </c>
-      <c r="K16" s="23" t="s">
+      <c r="K16" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="24" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="E17" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" s="25">
+      <c r="F17" s="22">
         <v>-35.709999999999994</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="22">
         <v>-38.00999999999999</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="22">
         <v>0.75</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="22">
         <v>2.3</v>
       </c>
       <c r="J17" s="8">
         <v>3.07</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="K17" s="23" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="25">
+        <v>-38.00999999999999</v>
+      </c>
+      <c r="G18" s="25">
+        <v>-39.50999999999999</v>
+      </c>
+      <c r="H18" s="25">
+        <v>1.63</v>
+      </c>
+      <c r="I18" s="25">
+        <v>1.5</v>
+      </c>
+      <c r="J18" s="28">
+        <v>0.92</v>
+      </c>
+      <c r="K18" s="26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B19" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C19" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="30" t="s">
+      <c r="E19" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="28">
-        <v>-38.00999999999999</v>
-      </c>
-      <c r="G18" s="28">
+      <c r="F19" s="29">
         <v>-39.50999999999999</v>
       </c>
-      <c r="H18" s="28">
-        <v>1.63</v>
-      </c>
-      <c r="I18" s="28">
-        <v>1.5</v>
-      </c>
-      <c r="J18" s="31">
-        <v>0.92</v>
-      </c>
-      <c r="K18" s="29" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
+      <c r="G19" s="29">
+        <v>-45.099999999999994</v>
+      </c>
+      <c r="H19" s="29">
+        <v>9.33</v>
+      </c>
+      <c r="I19" s="29">
+        <v>5.59</v>
+      </c>
+      <c r="J19" s="28">
+        <v>0.6</v>
+      </c>
+      <c r="K19" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="34" t="s">
+    </row>
+    <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="F19" s="32">
-        <v>-39.50999999999999</v>
-      </c>
-      <c r="G19" s="32">
-        <v>-45.099999999999994</v>
-      </c>
-      <c r="H19" s="32">
-        <v>9.33</v>
-      </c>
-      <c r="I19" s="32">
-        <v>5.59</v>
-      </c>
-      <c r="J19" s="31">
-        <v>0.6</v>
-      </c>
-      <c r="K19" s="33" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
     </row>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1618,7 +1590,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1631,31 +1603,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1724,7 +1696,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1753,7 +1725,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1782,25 +1754,25 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D6" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="19">
         <v>-22.21</v>
       </c>
       <c r="F6" s="19">
-        <v>-26.71</v>
+        <v>-35.71</v>
       </c>
       <c r="G6" s="19">
-        <v>2.25</v>
+        <v>2.98</v>
       </c>
       <c r="H6" s="19">
-        <v>4.5</v>
+        <v>13.5</v>
       </c>
       <c r="I6" s="8">
-        <v>2</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1811,25 +1783,25 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-26.71</v>
+        <v>-35.71</v>
       </c>
       <c r="F7" s="22">
-        <v>-35.71</v>
+        <v>-38.01</v>
       </c>
       <c r="G7" s="22">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="H7" s="22">
-        <v>9</v>
-      </c>
-      <c r="I7" s="12">
-        <v>12.27</v>
+        <v>2.3</v>
+      </c>
+      <c r="I7" s="8">
+        <v>3.07</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1840,111 +1812,82 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-35.71</v>
+        <v>-38.01</v>
       </c>
       <c r="F8" s="25">
-        <v>-38.01</v>
+        <v>-39.51</v>
       </c>
       <c r="G8" s="25">
-        <v>0.75</v>
+        <v>1.63</v>
       </c>
       <c r="H8" s="25">
-        <v>2.3</v>
-      </c>
-      <c r="I8" s="8">
-        <v>3.07</v>
+        <v>1.5</v>
+      </c>
+      <c r="I8" s="28">
+        <v>0.92</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
+      <c r="A9" s="29">
         <v>8</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="28">
+      <c r="C9" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="29">
         <v>1</v>
       </c>
-      <c r="E9" s="28">
-        <v>-38.01</v>
-      </c>
-      <c r="F9" s="28">
+      <c r="E9" s="29">
         <v>-39.51</v>
       </c>
-      <c r="G9" s="28">
-        <v>1.63</v>
-      </c>
-      <c r="H9" s="28">
-        <v>1.5</v>
-      </c>
-      <c r="I9" s="31">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
+      <c r="F9" s="29">
+        <v>-45.1</v>
+      </c>
+      <c r="G9" s="29">
+        <v>9.33</v>
+      </c>
+      <c r="H9" s="29">
+        <v>5.59</v>
+      </c>
+      <c r="I9" s="28">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="32">
-        <v>1</v>
-      </c>
-      <c r="E10" s="32">
-        <v>-39.51</v>
-      </c>
-      <c r="F10" s="32">
+      <c r="C10" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="34">
+        <v>9</v>
+      </c>
+      <c r="E10" s="34">
+        <v>-1.31</v>
+      </c>
+      <c r="F10" s="34">
         <v>-45.1</v>
       </c>
-      <c r="G10" s="32">
-        <v>9.33</v>
-      </c>
-      <c r="H10" s="32">
-        <v>5.59</v>
-      </c>
-      <c r="I10" s="31">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="37">
-        <v>9</v>
-      </c>
-      <c r="E11" s="37">
-        <v>-1.31</v>
-      </c>
-      <c r="F11" s="37">
-        <v>-45.1</v>
-      </c>
-      <c r="G11" s="37">
+      <c r="G10" s="34">
         <v>20.95</v>
       </c>
-      <c r="H11" s="37">
+      <c r="H10" s="34">
         <v>43.79</v>
       </c>
-      <c r="I11" s="37">
+      <c r="I10" s="34">
         <v>2.09</v>
       </c>
     </row>

--- a/SGC-CKN/Excel/12bd2238-5dc8-459d-a641-da6acac5da71_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-30_D800_23-03-2026.xlsx
+++ b/SGC-CKN/Excel/12bd2238-5dc8-459d-a641-da6acac5da71_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-30_D800_23-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="73">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t/>
+    <t>SGCT-KCN0004</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -149,6 +149,9 @@
   <si>
     <t xml:space="preserve">17h30
 21/03/2026</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>5</t>
@@ -1317,24 +1320,24 @@
         <v>3.04</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F15" s="19">
         <v>-22.21</v>
@@ -1352,24 +1355,24 @@
         <v>2</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F16" s="19">
         <v>-26.71</v>
@@ -1387,24 +1390,24 @@
         <v>12.27</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F17" s="22">
         <v>-35.709999999999994</v>
@@ -1427,19 +1430,19 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F18" s="25">
         <v>-38.00999999999999</v>
@@ -1462,19 +1465,19 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B19" s="29" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F19" s="29">
         <v>-39.50999999999999</v>
@@ -1492,12 +1495,12 @@
         <v>0.6</v>
       </c>
       <c r="K19" s="30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B22" s="32"/>
       <c r="C22" s="32"/>
@@ -1603,31 +1606,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1754,7 +1757,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" s="19">
         <v>2</v>
@@ -1783,7 +1786,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1812,7 +1815,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1841,7 +1844,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" s="29">
         <v>1</v>
@@ -1864,13 +1867,13 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D10" s="34">
         <v>9</v>
